--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>9054003184.0</t>
+          <t>9054003184</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>395003.0</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>9054003184</t>
+          <t>9054003184.0</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -15637,7 +15637,7 @@
       </c>
       <c r="H230" s="5" t="inlineStr">
         <is>
-          <t>9879748692.0</t>
+          <t>9879748692</t>
         </is>
       </c>
       <c r="I230" s="5" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="K230" s="5" t="inlineStr">
         <is>
-          <t>395003.0</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L230" s="5" t="inlineStr">
@@ -35776,7 +35776,7 @@
       </c>
       <c r="M535" s="10" t="inlineStr">
         <is>
-          <t>anganwadi na 2 yers complete nathi</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N535" s="11" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="M588" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N588" s="11" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="M609" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N609" s="11" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="M614" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N614" s="11" t="inlineStr">
@@ -42933,7 +42933,7 @@
       </c>
       <c r="H644" s="5" t="inlineStr">
         <is>
-          <t>7405759272</t>
+          <t>7405759272.0</t>
         </is>
       </c>
       <c r="I644" s="5" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="K644" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L644" s="5" t="inlineStr">
@@ -42999,7 +42999,7 @@
       </c>
       <c r="H645" s="5" t="inlineStr">
         <is>
-          <t>7016757300</t>
+          <t>7016757300.0</t>
         </is>
       </c>
       <c r="I645" s="5" t="inlineStr">
@@ -43014,7 +43014,7 @@
       </c>
       <c r="K645" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>395001.0</t>
         </is>
       </c>
       <c r="L645" s="5" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="M695" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N695" s="11" t="inlineStr">
@@ -47057,7 +47057,7 @@
       </c>
       <c r="H707" s="5" t="inlineStr">
         <is>
-          <t>9974238362</t>
+          <t>9974238362.0</t>
         </is>
       </c>
       <c r="I707" s="5" t="inlineStr">
@@ -47072,7 +47072,7 @@
       </c>
       <c r="K707" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>395010.0</t>
         </is>
       </c>
       <c r="L707" s="5" t="inlineStr">
@@ -47189,7 +47189,7 @@
       </c>
       <c r="H709" s="5" t="inlineStr">
         <is>
-          <t>9016060797</t>
+          <t>9016060797.0</t>
         </is>
       </c>
       <c r="I709" s="5" t="inlineStr">
@@ -47204,7 +47204,7 @@
       </c>
       <c r="K709" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L709" s="5" t="inlineStr">
@@ -47278,10 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="10" t="inlineStr"/>
-      <c r="N710" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M710" s="6" t="inlineStr">
+        <is>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
+        </is>
+      </c>
+      <c r="N710" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
@@ -47379,7 +47383,7 @@
       </c>
       <c r="H712" s="5" t="inlineStr">
         <is>
-          <t>7575882644</t>
+          <t>7575882644.0</t>
         </is>
       </c>
       <c r="I712" s="5" t="inlineStr">
@@ -47394,7 +47398,7 @@
       </c>
       <c r="K712" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>395002.0</t>
         </is>
       </c>
       <c r="L712" s="5" t="inlineStr">
@@ -47441,7 +47445,7 @@
       </c>
       <c r="H713" s="5" t="inlineStr">
         <is>
-          <t>9898227239</t>
+          <t>9898227239.0</t>
         </is>
       </c>
       <c r="I713" s="5" t="inlineStr">
@@ -47456,7 +47460,7 @@
       </c>
       <c r="K713" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>395002.0</t>
         </is>
       </c>
       <c r="L713" s="5" t="inlineStr">
@@ -47503,7 +47507,7 @@
       </c>
       <c r="H714" s="5" t="inlineStr">
         <is>
-          <t>9173178411</t>
+          <t>9173178411.0</t>
         </is>
       </c>
       <c r="I714" s="5" t="inlineStr">
@@ -47518,7 +47522,7 @@
       </c>
       <c r="K714" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L714" s="5" t="inlineStr">
@@ -47569,7 +47573,7 @@
       </c>
       <c r="H715" s="5" t="inlineStr">
         <is>
-          <t>9737925588</t>
+          <t>9737925588.0</t>
         </is>
       </c>
       <c r="I715" s="5" t="inlineStr">
@@ -47584,7 +47588,7 @@
       </c>
       <c r="K715" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>395009.0</t>
         </is>
       </c>
       <c r="L715" s="5" t="inlineStr">
@@ -47635,7 +47639,7 @@
       </c>
       <c r="H716" s="5" t="inlineStr">
         <is>
-          <t>9537569976</t>
+          <t>9537569976.0</t>
         </is>
       </c>
       <c r="I716" s="5" t="inlineStr">
@@ -47650,7 +47654,7 @@
       </c>
       <c r="K716" s="5" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>395004.0</t>
         </is>
       </c>
       <c r="L716" s="5" t="inlineStr">
@@ -47701,7 +47705,7 @@
       </c>
       <c r="H717" s="5" t="inlineStr">
         <is>
-          <t>9727056910</t>
+          <t>9727056910.0</t>
         </is>
       </c>
       <c r="I717" s="5" t="inlineStr">
@@ -47716,7 +47720,7 @@
       </c>
       <c r="K717" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>395002.0</t>
         </is>
       </c>
       <c r="L717" s="5" t="inlineStr">
@@ -47767,7 +47771,7 @@
       </c>
       <c r="H718" s="5" t="inlineStr">
         <is>
-          <t>7990957891</t>
+          <t>7990957891.0</t>
         </is>
       </c>
       <c r="I718" s="5" t="inlineStr">
@@ -47782,7 +47786,7 @@
       </c>
       <c r="K718" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>395002.0</t>
         </is>
       </c>
       <c r="L718" s="5" t="inlineStr">
@@ -47833,7 +47837,7 @@
       </c>
       <c r="H719" s="5" t="inlineStr">
         <is>
-          <t>9978685820</t>
+          <t>9978685820.0</t>
         </is>
       </c>
       <c r="I719" s="5" t="inlineStr">
@@ -47848,7 +47852,7 @@
       </c>
       <c r="K719" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L719" s="5" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -15637,7 +15637,7 @@
       </c>
       <c r="H230" s="5" t="inlineStr">
         <is>
-          <t>9879748692</t>
+          <t>9879748692.0</t>
         </is>
       </c>
       <c r="I230" s="5" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="K230" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L230" s="5" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,11 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -131,12 +126,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -942,37 +931,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>6353938435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1038,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1202,37 +1191,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>9978260385</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>BEGUMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1257,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>HASHMIRA CHANDKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8460673067</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>BHATHENA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1924,37 +1913,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>MAHERA SALIM SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>9033552557</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2107,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3266,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4718,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4784,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6662,37 +6651,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>8758147466</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6717,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>RAIHAN SAEED PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>7405759272</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>rander</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7022,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7682,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8176,37 +8165,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8231,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9485,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>ALIAN MO.ARIF ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>8488990883</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9683,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>9879814246</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>TURKIWAD MUGLISARA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>NANAVAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10156,37 +10145,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>6354501628</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>VARYAVI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10607,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>UMMEHAANI ASHFAQUE SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>8160140266</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10871,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10937,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>VOHRAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11663,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>9825956199</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>RANITALAW</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11729,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>9173442244</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12059,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12125,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12323,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>AFIYA ASIFMIYA KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>9925523296</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13222,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13324,37 +13313,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>AAYAT IMRAN SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>9879068344</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14076,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14472,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14508,37 +14497,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>INAYA IMRAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>7990106539</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15068,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16124,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16292,37 +16281,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>9601903640</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA MOMNAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16611,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED GULAHMED PANWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>7405251413</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16786,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17086,37 +17075,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>NABILA BANU AHMED NOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17152,37 +17141,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>NABILABANU AHMEDNOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17599,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>9727048923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>SACHIN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>394230</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>SURAT CITY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18164,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18398,37 +18387,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>9898377514</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19443,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>HAMJA SAKIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>9510628797</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>395023</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19773,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>9898710533</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>RAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20144,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20378,37 +20367,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20444,37 +20433,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21034,37 +21023,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>9510956369</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>KADARSHAH NI NAAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21328,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21364,37 +21353,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>AAHIL ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21430,37 +21419,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21856,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22710,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22878,37 +22867,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>7041239541</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>NAVSARI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23197,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>8401189493</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23461,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>9081019408</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23725,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>ZAINAB IKBALKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>7016137650</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23832,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24792,37 +24781,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>6359658865</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25350,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25416,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25452,37 +25441,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25507,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26600,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26768,37 +26757,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26864,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26900,37 +26889,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27021,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>SHAAD ALI FAIZAL JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>9979765038</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27128,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27194,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27260,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27326,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28114,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29038,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29104,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29170,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29632,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30064,37 +30053,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>7802820848</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>NEAR HAJURI CHAMBERS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30581,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>9586110486</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>Bela Industrial Estate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30856,37 +30845,37 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>UMAIR AYAZUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
         <is>
-          <t>9998709823</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I461" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31120,37 +31109,37 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>SHIFA IRFAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
         <is>
-          <t>9714226593</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I465" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31318,37 +31307,37 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>NIMRA MOHSIN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>8140864087</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>KADAR SHAH NI NAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L468" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31384,37 +31373,37 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>FAIZAN HUSAIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
         <is>
-          <t>8000435667</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32102,37 +32091,37 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L480" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32234,37 +32223,37 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32300,37 +32289,37 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32564,37 +32553,37 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>ANAYA MO.AZHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>9724345673</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I487" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32894,37 +32883,37 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>VIANSH DIVYESHKUMAR SONDARVA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>9825120985</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>ZAMPA BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L492" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33784,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34630,37 +34619,37 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>NOUMAN SAIYED ALI SAIYED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>9327540050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K518" s="5" t="inlineStr">
         <is>
-          <t>392003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35252,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35482,37 +35471,37 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35746,42 +35735,42 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>RABIYA JAFARKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
         <is>
-          <t>9979551351</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I535" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
-        </is>
-      </c>
-      <c r="M535" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N535" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M535" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N535" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -36302,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36930,37 +36919,37 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37194,37 +37183,37 @@
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
-          <t>AHMED YAKUB MOTIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H557" s="5" t="inlineStr">
         <is>
-          <t>7203078688</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37656,37 +37645,37 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>AAYAT MOHAMMAD ASHRAF KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>8849059910</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>OPP. ALVI ROW HOUSE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K564" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37854,37 +37843,37 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>AISHA IMRAN MANSUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
         <is>
-          <t>7016269517</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38672,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39236,42 +39225,42 @@
       </c>
       <c r="G588" s="5" t="inlineStr">
         <is>
-          <t>ASHHAR MOHAMMED NASIM ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H588" s="5" t="inlineStr">
         <is>
-          <t>8264969600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I588" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J588" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K588" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L588" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
-        </is>
-      </c>
-      <c r="M588" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N588" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M588" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N588" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -40622,42 +40611,42 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>HASNAIN ISTIYAK SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
         <is>
-          <t>9586438778</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I609" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J609" s="5" t="inlineStr">
         <is>
-          <t>SHERALIBAVA NI DARGAH NO VISHTAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K609" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
-        </is>
-      </c>
-      <c r="M609" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N609" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M609" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N609" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -40952,42 +40941,42 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>SAIIMA SAMIR PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>8347012249</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I614" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
-        </is>
-      </c>
-      <c r="M614" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N614" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M614" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N614" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43522,37 +43511,37 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>RIDAZAHRA MOHAMMAD YUSUF PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
         <is>
-          <t>9712007037</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I653" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43816,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43918,37 +43907,37 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>NOOR FATEMA MO TOFIK MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>8460333425</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I659" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
-          <t>MURAGVAN TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44464,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45094,37 +45083,37 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>ANABIA SALMAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
-          <t>9687908092</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I677" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J677" s="5" t="inlineStr">
         <is>
-          <t>SHAHPORE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K677" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45256,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45490,37 +45479,37 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>ABHAY ASHOK PENDHARKAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
         <is>
-          <t>8141172225</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I683" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K683" s="5" t="inlineStr">
         <is>
-          <t>395017</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45652,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45718,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45820,37 +45809,37 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>MAHERABANU AMIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
         <is>
-          <t>9974238362</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I688" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>SAHARADARVAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K688" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45982,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46018,37 +46007,37 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>AEMAN KAMIL SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
         <is>
-          <t>7777993155</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I691" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J691" s="5" t="inlineStr">
         <is>
-          <t>SAHARA DAEWAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K691" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46274,42 +46263,42 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>ARAV SURESH RATHOD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
         <is>
-          <t>9825274436</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I695" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J695" s="5" t="inlineStr">
         <is>
-          <t>MALBARI SAHEB NO TEKRO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L695" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
-        </is>
-      </c>
-      <c r="M695" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N695" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M695" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N695" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -47118,37 +47107,37 @@
       </c>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>SUFIYANKHAN IRFAN KHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
         <is>
-          <t>8799617761</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I708" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J708" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K708" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L708" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47250,42 +47239,42 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>SHAHID HUSAIN MUJAFFARHUSEN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
         <is>
-          <t>6351802600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I710" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J710" s="5" t="inlineStr">
         <is>
-          <t>Kamela Main Road,Salabatpura,Surat</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L710" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M710" s="6" t="inlineStr">
-        <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
-        </is>
-      </c>
-      <c r="N710" s="7" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M710" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+        </is>
+      </c>
+      <c r="N710" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -47346,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -126,6 +131,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -961,7 +972,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1038,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1232,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1298,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1888,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1913,37 +1924,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAHERA SALIM SHAIKH</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9033552557</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2107,37 +2118,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOMAN MOHSIN PINJARI</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879049881</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3266,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4718,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4784,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6692,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6758,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7022,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7682,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8206,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8231,37 +8242,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9485,37 +9496,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALIAN MO.ARIF ANSARI</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8488990883</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYEDPURA</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9683,37 +9694,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879814246</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TURKIWAD MUGLISARA</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANAVAT</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10145,37 +10156,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6354501628</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VARYAVI BAZAR</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10607,37 +10618,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMMEHAANI ASHFAQUE SHAH</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8160140266</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10912,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10978,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11704,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11770,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12100,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12125,37 +12136,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12323,37 +12334,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AFIYA ASIFMIYA KHARADI</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9925523296</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13222,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13313,37 +13324,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAYAT IMRAN SHAH</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879068344</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14076,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14472,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14538,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15068,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16124,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16322,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16611,37 +16622,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED GULAHMED PANWALA</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405251413</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16786,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17075,37 +17086,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILA BANU AHMED NOOR SHAIKH</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17141,37 +17152,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILABANU AHMEDNOOR SHAIKH</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17599,37 +17610,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9727048923</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SACHIN</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394230</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SURAT CITY</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18164,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18428,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19484,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19814,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20144,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20367,37 +20378,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20433,37 +20444,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21023,37 +21034,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510956369</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KADARSHAH NI NAAL</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21328,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21353,37 +21364,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21460,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21856,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22710,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22908,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23238,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23461,37 +23472,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9081019408</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23725,37 +23736,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZAINAB IKBALKHAN PATHAN</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7016137650</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395004</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23832,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24781,37 +24792,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6359658865</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25350,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25416,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25482,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25548,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26600,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26798,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26889,37 +26900,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27021,37 +27032,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAAD ALI FAIZAL JARIWALA</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9979765038</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27128,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27194,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27260,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27326,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28114,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29038,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29104,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29170,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30053,37 +30064,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7802820848</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR HAJURI CHAMBERS</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30581,37 +30592,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9586110486</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bela Industrial Estate</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30845,37 +30856,37 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMAIR AYAZUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9998709823</t>
         </is>
       </c>
       <c r="I461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394107</t>
         </is>
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31150,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31307,37 +31318,37 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NIMRA MOHSIN PATHAN</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8140864087</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KADAR SHAH NI NAL</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31373,37 +31384,37 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FAIZAN HUSAIN SHAIKH</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8000435667</t>
         </is>
       </c>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUSTAMPURA</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32091,37 +32102,37 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AJIJA ZAHIR SHAIKH</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825185512</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHIMANI TEKARO JUNA DEPO</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32223,37 +32234,37 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARISH AZAHARUDDIN MUJAWAR</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9909812786</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR TANTWAD MASJID</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32289,37 +32300,37 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARISH AZAHARUDDIN MUJAWAR</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9909812786</t>
         </is>
       </c>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR TANTWAD MASJID</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32594,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32883,37 +32894,37 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIANSH DIVYESHKUMAR SONDARVA</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825120985</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZAMPA BAZAR</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33784,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34619,37 +34630,37 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOUMAN SAIYED ALI SAIYED</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9327540050</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYEDPURA</t>
         </is>
       </c>
       <c r="K518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>392003</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35252,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35471,37 +35482,37 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOMAN MOHSIN PINJARI</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879049881</t>
         </is>
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35735,42 +35746,42 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RABIYA JAFARKHAN PATHAN</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9979551351</t>
         </is>
       </c>
       <c r="I535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M535" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
-        </is>
-      </c>
-      <c r="N535" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>UMARWADA</t>
+        </is>
+      </c>
+      <c r="M535" s="10" t="inlineStr">
+        <is>
+          <t>anganwadi na 2 yers complete nathi</t>
+        </is>
+      </c>
+      <c r="N535" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -36291,7 +36302,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36960,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37183,37 +37194,37 @@
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AHMED YAKUB MOTIWALA</t>
         </is>
       </c>
       <c r="H557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7203078688</t>
         </is>
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37645,37 +37656,37 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAYAT MOHAMMAD ASHRAF KHARADI</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8849059910</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OPP. ALVI ROW HOUSE</t>
         </is>
       </c>
       <c r="K564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37843,37 +37854,37 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AISHA IMRAN MANSUR</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7016269517</t>
         </is>
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395005</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -39225,42 +39236,42 @@
       </c>
       <c r="G588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASHHAR MOHAMMED NASIM ANSARI</t>
         </is>
       </c>
       <c r="H588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8264969600</t>
         </is>
       </c>
       <c r="I588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L588" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M588" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
-        </is>
-      </c>
-      <c r="N588" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>Unn</t>
+        </is>
+      </c>
+      <c r="M588" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N588" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -40611,42 +40622,42 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HASNAIN ISTIYAK SHEKH</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9586438778</t>
         </is>
       </c>
       <c r="I609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHERALIBAVA NI DARGAH NO VISHTAR</t>
         </is>
       </c>
       <c r="K609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M609" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
-        </is>
-      </c>
-      <c r="N609" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SAGRAMPURA</t>
+        </is>
+      </c>
+      <c r="M609" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N609" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -40971,7 +40982,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43090,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43511,37 +43522,37 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RIDAZAHRA MOHAMMAD YUSUF PATHAN</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9712007037</t>
         </is>
       </c>
       <c r="I653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43907,37 +43918,37 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOOR FATEMA MO TOFIK MANSURI</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460333425</t>
         </is>
       </c>
       <c r="I659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MURAGVAN TEKRA</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -45113,7 +45124,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45641,7 +45652,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45718,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45971,7 +45982,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46007,37 +46018,37 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AEMAN KAMIL SHEKH</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7777993155</t>
         </is>
       </c>
       <c r="I691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAHARA DAEWAJA</t>
         </is>
       </c>
       <c r="K691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395010</t>
         </is>
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46263,42 +46274,42 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARAV SURESH RATHOD</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825274436</t>
         </is>
       </c>
       <c r="I695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MALBARI SAHEB NO TEKRO</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M695" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
-        </is>
-      </c>
-      <c r="N695" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SAGRAMPURA</t>
+        </is>
+      </c>
+      <c r="M695" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N695" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -47137,7 +47148,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47280,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6353938435</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9978260385</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGUMPURA</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1268,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HASHMIRA CHANDKHAN PATHAN</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460673067</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATHENA</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>Status not found</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -6662,37 +6662,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8758147466</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6728,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAIHAN SAEED PATEL</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405759272</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>rander</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395005</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -8176,37 +8176,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -10882,37 +10882,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VOHRAWAD</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11674,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825956199</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANITALAW</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11740,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9173442244</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12070,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INAYA IMRAN SHAIKH</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7990106539</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -16292,37 +16292,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9601903640</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA MOMNAWAD</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -18398,37 +18398,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898377514</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19454,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HAMJA SAKIR SHAIKH</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510628797</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395023</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19784,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898710533</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAMPURA</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -21430,37 +21430,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -22878,37 +22878,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7041239541</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NAVSARI BAZAR</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23208,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8401189493</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -25452,37 +25452,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25518,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26768,37 +26768,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -31120,37 +31120,37 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHIFA IRFAN PATHAN</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9714226593</t>
         </is>
       </c>
       <c r="I465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -32564,37 +32564,37 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANAYA MO.AZHAR SHAIKH</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9724345673</t>
         </is>
       </c>
       <c r="I487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -36930,37 +36930,37 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AJIJA ZAHIR SHAIKH</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825185512</t>
         </is>
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHIMANI TEKARO JUNA DEPO</t>
         </is>
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -40952,42 +40952,42 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIIMA SAMIR PATEL</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8347012249</t>
         </is>
       </c>
       <c r="I614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394107</t>
         </is>
       </c>
       <c r="L614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M614" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N614" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>KOSAD</t>
+        </is>
+      </c>
+      <c r="M614" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N614" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43816,7 +43816,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -44464,7 +44464,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45094,37 +45094,37 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANABIA SALMAN SHAIKH</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9687908092</t>
         </is>
       </c>
       <c r="I677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAHPORE</t>
         </is>
       </c>
       <c r="K677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45256,7 +45256,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45490,37 +45490,37 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ABHAY ASHOK PENDHARKAR</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141172225</t>
         </is>
       </c>
       <c r="I683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATAR</t>
         </is>
       </c>
       <c r="K683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395017</t>
         </is>
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATAR</t>
         </is>
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45820,37 +45820,37 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAHERABANU AMIN SHAIKH</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9974238362</t>
         </is>
       </c>
       <c r="I688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAHARADARVAJA</t>
         </is>
       </c>
       <c r="K688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395010</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -47118,37 +47118,37 @@
       </c>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SUFIYANKHAN IRFAN KHAN</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8799617761</t>
         </is>
       </c>
       <c r="I708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUSTAMPURA</t>
         </is>
       </c>
       <c r="K708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47250,42 +47250,42 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAHID HUSAIN MUJAFFARHUSEN SHAIKH</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6351802600</t>
         </is>
       </c>
       <c r="I710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kamela Main Road,Salabatpura,Surat</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M710" s="8" t="inlineStr">
-        <is>
-          <t>Status not found</t>
-        </is>
-      </c>
-      <c r="N710" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M710" s="6" t="inlineStr">
+        <is>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ  પ્રથમ  રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N710" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>
@@ -47346,7 +47346,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N719"/>
+  <dimension ref="A1:N720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -47871,6 +47871,72 @@
         </is>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" s="4" t="n">
+        <v>46147.1119777662</v>
+      </c>
+      <c r="B720" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C720" s="5" t="inlineStr">
+        <is>
+          <t>GJ/2026-27/SRC/2176392</t>
+        </is>
+      </c>
+      <c r="D720" s="4" t="n">
+        <v>43757</v>
+      </c>
+      <c r="E720" s="5" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="F720" s="5" t="inlineStr">
+        <is>
+          <t>19-10-2019</t>
+        </is>
+      </c>
+      <c r="G720" s="5" t="inlineStr">
+        <is>
+          <t>AAFIYA FATEMA GULAM KASIM BHORANIYA</t>
+        </is>
+      </c>
+      <c r="H720" s="5" t="inlineStr">
+        <is>
+          <t>8980858586</t>
+        </is>
+      </c>
+      <c r="I720" s="5" t="inlineStr">
+        <is>
+          <t>GIRL</t>
+        </is>
+      </c>
+      <c r="J720" s="5" t="inlineStr">
+        <is>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="K720" s="5" t="inlineStr">
+        <is>
+          <t>395003</t>
+        </is>
+      </c>
+      <c r="L720" s="5" t="inlineStr">
+        <is>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M720" s="6" t="inlineStr">
+        <is>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ  પ્રથમ  રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N720" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47903,7 +47903,7 @@
       </c>
       <c r="H720" s="5" t="inlineStr">
         <is>
-          <t>8980858586</t>
+          <t>8980858586.0</t>
         </is>
       </c>
       <c r="I720" s="5" t="inlineStr">
@@ -47918,7 +47918,7 @@
       </c>
       <c r="K720" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>395003.0</t>
         </is>
       </c>
       <c r="L720" s="5" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>6353938435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6353938435</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="M588" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N588" s="11" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="M609" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N609" s="11" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="M614" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N614" s="11" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="M695" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N695" s="11" t="inlineStr">
@@ -47280,7 +47280,7 @@
       </c>
       <c r="M710" s="6" t="inlineStr">
         <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ  પ્રથમ  રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
         </is>
       </c>
       <c r="N710" s="7" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47278,14 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="6" t="inlineStr">
-        <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
-        </is>
-      </c>
-      <c r="N710" s="7" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
+      <c r="M710" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N710" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="M588" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N588" s="11" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="M609" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N609" s="11" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="M614" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N614" s="11" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="M695" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N695" s="11" t="inlineStr">
@@ -47280,7 +47280,7 @@
       </c>
       <c r="M710" s="10" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
         </is>
       </c>
       <c r="N710" s="11" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>6353938435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>9978260385</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>BEGUMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1268,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>HASHMIRA CHANDKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8460673067</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>BHATHENA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1924,37 +1924,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>MAHERA SALIM SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>9033552557</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2118,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6662,37 +6662,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>8758147466</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6728,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>RAIHAN SAEED PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>7405759272</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>rander</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8176,37 +8176,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8242,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9496,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>ALIAN MO.ARIF ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>8488990883</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9694,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>9879814246</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>TURKIWAD MUGLISARA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>NANAVAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10156,37 +10156,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>6354501628</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>VARYAVI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10618,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>UMMEHAANI ASHFAQUE SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>8160140266</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10882,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>VOHRAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11674,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>9825956199</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>RANITALAW</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11740,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>9173442244</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12070,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12136,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12334,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>AFIYA ASIFMIYA KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>9925523296</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13324,37 +13324,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>AAYAT IMRAN SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>9879068344</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>INAYA IMRAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>7990106539</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16292,37 +16292,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>9601903640</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA MOMNAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16622,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED GULAHMED PANWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>7405251413</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17086,37 +17086,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>NABILA BANU AHMED NOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17152,37 +17152,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>NABILABANU AHMEDNOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17610,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>9727048923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>SACHIN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>394230</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>SURAT CITY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18398,37 +18398,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>9898377514</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19454,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>HAMJA SAKIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>9510628797</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>395023</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19784,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>9898710533</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>RAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20378,37 +20378,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20444,37 +20444,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21034,37 +21034,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>9510956369</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>KADARSHAH NI NAAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21364,37 +21364,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>AAHIL ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21430,37 +21430,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22878,37 +22878,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>7041239541</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>NAVSARI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23208,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>8401189493</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23472,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>9081019408</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23736,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>ZAINAB IKBALKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>7016137650</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24792,37 +24792,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>6359658865</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25452,37 +25452,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25518,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26768,37 +26768,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26900,37 +26900,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27032,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>SHAAD ALI FAIZAL JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>9979765038</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30064,37 +30064,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>7802820848</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>NEAR HAJURI CHAMBERS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30592,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>9586110486</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>Bela Industrial Estate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6353938435</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9978260385</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGUMPURA</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1268,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HASHMIRA CHANDKHAN PATHAN</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460673067</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATHENA</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1924,37 +1924,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAHERA SALIM SHAIKH</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9033552557</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2118,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOMAN MOHSIN PINJARI</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879049881</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6662,37 +6662,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8758147466</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6728,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAIHAN SAEED PATEL</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405759272</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>rander</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395005</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8176,37 +8176,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8242,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9496,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALIAN MO.ARIF ANSARI</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8488990883</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYEDPURA</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9694,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879814246</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TURKIWAD MUGLISARA</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANAVAT</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10156,37 +10156,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6354501628</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VARYAVI BAZAR</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10618,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMMEHAANI ASHFAQUE SHAH</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8160140266</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10882,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VOHRAWAD</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11674,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825956199</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANITALAW</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11740,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9173442244</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12070,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12136,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12334,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AFIYA ASIFMIYA KHARADI</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9925523296</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13324,37 +13324,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAYAT IMRAN SHAH</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879068344</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INAYA IMRAN SHAIKH</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7990106539</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16292,37 +16292,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9601903640</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA MOMNAWAD</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16622,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED GULAHMED PANWALA</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405251413</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17086,37 +17086,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILA BANU AHMED NOOR SHAIKH</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17152,37 +17152,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILABANU AHMEDNOOR SHAIKH</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17610,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9727048923</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SACHIN</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394230</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SURAT CITY</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18398,37 +18398,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898377514</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19454,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HAMJA SAKIR SHAIKH</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510628797</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395023</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19784,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898710533</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAMPURA</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20378,37 +20378,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20444,37 +20444,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21034,37 +21034,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510956369</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KADARSHAH NI NAAL</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21364,37 +21364,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21430,37 +21430,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22878,37 +22878,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7041239541</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NAVSARI BAZAR</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23208,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8401189493</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23472,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9081019408</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23736,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZAINAB IKBALKHAN PATHAN</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7016137650</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395004</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24792,37 +24792,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6359658865</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25452,37 +25452,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25518,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26768,37 +26768,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26900,37 +26900,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27032,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAAD ALI FAIZAL JARIWALA</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9979765038</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30064,37 +30064,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7802820848</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR HAJURI CHAMBERS</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30592,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9586110486</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bela Industrial Estate</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47278,14 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="10" t="inlineStr">
-        <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
-        </is>
-      </c>
-      <c r="N710" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M710" s="6" t="inlineStr">
+        <is>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
+        </is>
+      </c>
+      <c r="N710" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N12" s="11" t="inlineStr">
@@ -39266,7 +39266,7 @@
       </c>
       <c r="M588" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N588" s="11" t="inlineStr">
@@ -40652,7 +40652,7 @@
       </c>
       <c r="M609" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N609" s="11" t="inlineStr">
@@ -40982,7 +40982,7 @@
       </c>
       <c r="M614" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N614" s="11" t="inlineStr">
@@ -46304,7 +46304,7 @@
       </c>
       <c r="M695" s="10" t="inlineStr">
         <is>
-          <t>આપે શાળાઓ ની પુનઃ પસંદગી કરેલ નથી.</t>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
         </is>
       </c>
       <c r="N695" s="11" t="inlineStr">
@@ -47280,7 +47280,7 @@
       </c>
       <c r="M710" s="6" t="inlineStr">
         <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.</t>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ બીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
         </is>
       </c>
       <c r="N710" s="7" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47278,14 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="6" t="inlineStr">
-        <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ બીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
-        </is>
-      </c>
-      <c r="N710" s="7" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
+      <c r="M710" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N710" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>6353938435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>9978260385</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>BEGUMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1268,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>HASHMIRA CHANDKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8460673067</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>BHATHENA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1924,37 +1924,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>MAHERA SALIM SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>9033552557</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2118,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6662,37 +6662,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>8758147466</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6728,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>RAIHAN SAEED PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>7405759272</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>rander</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8176,37 +8176,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8242,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9496,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>ALIAN MO.ARIF ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>8488990883</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9694,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>9879814246</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>TURKIWAD MUGLISARA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>NANAVAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10156,37 +10156,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>6354501628</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>VARYAVI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10618,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>UMMEHAANI ASHFAQUE SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>8160140266</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10882,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>VOHRAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11674,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>9825956199</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>RANITALAW</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11740,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>9173442244</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12070,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12136,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12334,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>AFIYA ASIFMIYA KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>9925523296</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13324,37 +13324,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>AAYAT IMRAN SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>9879068344</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -17152,37 +17152,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>NABILABANU AHMEDNOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -18398,37 +18398,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>9898377514</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19454,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>HAMJA SAKIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>9510628797</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>395023</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19784,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>9898710533</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>RAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20378,37 +20378,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -21034,37 +21034,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>9510956369</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>KADARSHAH NI NAAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21430,37 +21430,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22878,37 +22878,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>7041239541</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>NAVSARI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23208,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>8401189493</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23472,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>9081019408</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23736,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>ZAINAB IKBALKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>7016137650</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24792,37 +24792,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>6359658865</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25452,37 +25452,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25518,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26900,37 +26900,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27032,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>SHAAD ALI FAIZAL JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>9979765038</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30064,37 +30064,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>7802820848</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>NEAR HAJURI CHAMBERS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30592,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>9586110486</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>Bela Industrial Estate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30856,37 +30856,37 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>UMAIR AYAZUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
         <is>
-          <t>9998709823</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I461" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31120,37 +31120,37 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>SHIFA IRFAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
         <is>
-          <t>9714226593</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I465" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31318,37 +31318,37 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>NIMRA MOHSIN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>8140864087</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>KADAR SHAH NI NAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L468" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31384,37 +31384,37 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>FAIZAN HUSAIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
         <is>
-          <t>8000435667</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32102,37 +32102,37 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L480" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32234,37 +32234,37 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32300,37 +32300,37 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32564,37 +32564,37 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>ANAYA MO.AZHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>9724345673</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I487" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32894,37 +32894,37 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>VIANSH DIVYESHKUMAR SONDARVA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>9825120985</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>ZAMPA BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L492" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34630,37 +34630,37 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>NOUMAN SAIYED ALI SAIYED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>9327540050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K518" s="5" t="inlineStr">
         <is>
-          <t>392003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -37194,37 +37194,37 @@
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
-          <t>AHMED YAKUB MOTIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H557" s="5" t="inlineStr">
         <is>
-          <t>7203078688</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37656,37 +37656,37 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>AAYAT MOHAMMAD ASHRAF KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>8849059910</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>OPP. ALVI ROW HOUSE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K564" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37854,37 +37854,37 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>AISHA IMRAN MANSUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
         <is>
-          <t>7016269517</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -43918,37 +43918,37 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>NOOR FATEMA MO TOFIK MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>8460333425</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I659" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
-          <t>MURAGVAN TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44464,7 +44464,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45094,37 +45094,37 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>ANABIA SALMAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
-          <t>9687908092</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I677" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J677" s="5" t="inlineStr">
         <is>
-          <t>SHAHPORE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K677" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45256,7 +45256,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45490,37 +45490,37 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>ABHAY ASHOK PENDHARKAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
         <is>
-          <t>8141172225</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I683" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K683" s="5" t="inlineStr">
         <is>
-          <t>395017</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45652,7 +45652,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45820,37 +45820,37 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>MAHERABANU AMIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
         <is>
-          <t>9974238362</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I688" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>SAHARADARVAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K688" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45982,7 +45982,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46018,37 +46018,37 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>AEMAN KAMIL SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
         <is>
-          <t>7777993155</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I691" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J691" s="5" t="inlineStr">
         <is>
-          <t>SAHARA DAEWAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K691" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46274,42 +46274,42 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>ARAV SURESH RATHOD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
         <is>
-          <t>9825274436</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I695" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J695" s="5" t="inlineStr">
         <is>
-          <t>MALBARI SAHEB NO TEKRO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L695" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
-        </is>
-      </c>
-      <c r="M695" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N695" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M695" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N695" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -47118,37 +47118,37 @@
       </c>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>SUFIYANKHAN IRFAN KHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
         <is>
-          <t>8799617761</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I708" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J708" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K708" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L708" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47250,42 +47250,42 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>SHAHID HUSAIN MUJAFFARHUSEN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
         <is>
-          <t>6351802600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I710" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J710" s="5" t="inlineStr">
         <is>
-          <t>Kamela Main Road,Salabatpura,Surat</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L710" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M710" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N710" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M710" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N710" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -47346,7 +47346,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -1038,7 +1038,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1924,37 +1924,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAHERA SALIM SHAIKH</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9033552557</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2118,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOMAN MOHSIN PINJARI</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879049881</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>INAYA IMRAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>7990106539</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16292,37 +16292,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>9601903640</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA MOMNAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16622,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED GULAHMED PANWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>7405251413</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17086,37 +17086,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>NABILA BANU AHMED NOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17610,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>9727048923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>SACHIN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>394230</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>SURAT CITY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -20444,37 +20444,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21364,37 +21364,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>AAHIL ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21430,37 +21430,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26768,37 +26768,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30094,7 +30094,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -31120,37 +31120,37 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHIFA IRFAN PATHAN</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9714226593</t>
         </is>
       </c>
       <c r="I465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -32924,7 +32924,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35482,37 +35482,37 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35746,42 +35746,42 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>RABIYA JAFARKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
         <is>
-          <t>9979551351</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I535" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
-        </is>
-      </c>
-      <c r="M535" s="10" t="inlineStr">
-        <is>
-          <t>anganwadi na 2 yers complete nathi</t>
-        </is>
-      </c>
-      <c r="N535" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M535" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N535" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36930,37 +36930,37 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37656,37 +37656,37 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAYAT MOHAMMAD ASHRAF KHARADI</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8849059910</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OPP. ALVI ROW HOUSE</t>
         </is>
       </c>
       <c r="K564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37854,37 +37854,37 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AISHA IMRAN MANSUR</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7016269517</t>
         </is>
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395005</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -40952,42 +40952,42 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>SAIIMA SAMIR PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>8347012249</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I614" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
-        </is>
-      </c>
-      <c r="M614" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N614" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M614" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+        </is>
+      </c>
+      <c r="N614" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43522,37 +43522,37 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>RIDAZAHRA MOHAMMAD YUSUF PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
         <is>
-          <t>9712007037</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I653" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43816,7 +43816,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45820,37 +45820,37 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MAHERABANU AMIN SHAIKH</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9974238362</t>
         </is>
       </c>
       <c r="I688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAHARADARVAJA</t>
         </is>
       </c>
       <c r="K688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395010</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45982,7 +45982,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46018,37 +46018,37 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AEMAN KAMIL SHEKH</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7777993155</t>
         </is>
       </c>
       <c r="I691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAHARA DAEWAJA</t>
         </is>
       </c>
       <c r="K691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395010</t>
         </is>
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46274,42 +46274,42 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARAV SURESH RATHOD</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825274436</t>
         </is>
       </c>
       <c r="I695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MALBARI SAHEB NO TEKRO</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L695" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M695" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N695" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SAGRAMPURA</t>
+        </is>
+      </c>
+      <c r="M695" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N695" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -47118,37 +47118,37 @@
       </c>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SUFIYANKHAN IRFAN KHAN</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8799617761</t>
         </is>
       </c>
       <c r="I708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUSTAMPURA</t>
         </is>
       </c>
       <c r="K708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L708" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47250,42 +47250,42 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAHID HUSAIN MUJAFFARHUSEN SHAIKH</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6351802600</t>
         </is>
       </c>
       <c r="I710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kamela Main Road,Salabatpura,Surat</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L710" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M710" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N710" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M710" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N710" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -47346,7 +47346,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -942,37 +942,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6353938435</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9978260385</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGUMPURA</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1268,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HASHMIRA CHANDKHAN PATHAN</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460673067</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATHENA</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>SALABATPURA</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6662,37 +6662,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8758147466</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6728,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAIHAN SAEED PATEL</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405759272</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>rander</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395005</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANDER</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8176,37 +8176,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8242,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898957851</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9496,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ALIAN MO.ARIF ANSARI</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8488990883</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYEDPURA</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9694,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879814246</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>TURKIWAD MUGLISARA</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANAVAT</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10156,37 +10156,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6354501628</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VARYAVI BAZAR</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10618,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMMEHAANI ASHFAQUE SHAH</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8160140266</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>DUMBHAL</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10882,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10948,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8087798621</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VOHRAWAD</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11674,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825956199</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANITALAW</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11740,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9173442244</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12070,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12136,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9638193923</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOMNAVAD</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12334,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AFIYA ASIFMIYA KHARADI</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9925523296</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13324,37 +13324,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAYAT IMRAN SHAH</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879068344</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14508,37 +14508,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INAYA IMRAN SHAIKH</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7990106539</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16292,37 +16292,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9601903640</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA MOMNAWAD</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16622,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMED GULAHMED PANWALA</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405251413</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17086,37 +17086,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILA BANU AHMED NOOR SHAIKH</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17152,37 +17152,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NABILABANU AHMEDNOOR SHAIKH</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141079302</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17610,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9727048923</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SACHIN</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394230</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SURAT CITY</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18398,37 +18398,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898377514</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19454,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HAMJA SAKIR SHAIKH</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510628797</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395023</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHESTAN</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19784,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9898710533</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RAMPURA</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20378,37 +20378,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20444,37 +20444,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9265929679</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BAVASIDI TEKRA</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21034,37 +21034,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9510956369</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KADARSHAH NI NAAL</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21364,37 +21364,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AAHIL ALMAS BHARUCHA</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7405183050</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGERWAD</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SODAGARWAD</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -22878,37 +22878,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7041239541</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NAVSARI BAZAR</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23208,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8401189493</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23472,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9081019408</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23736,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZAINAB IKBALKHAN PATHAN</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7016137650</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395004</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KATARGAM</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24792,37 +24792,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6359658865</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25452,37 +25452,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25518,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460770234</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26768,37 +26768,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26900,37 +26900,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9624460325</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNN</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unn</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27032,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAAD ALI FAIZAL JARIWALA</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9979765038</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27194,7 +27194,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27326,7 +27326,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29038,7 +29038,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30064,37 +30064,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7802820848</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR HAJURI CHAMBERS</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30592,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9586110486</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bela Industrial Estate</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SALABATPURA</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30856,37 +30856,37 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMAIR AYAZUDDIN SHAIKH</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9998709823</t>
         </is>
       </c>
       <c r="I461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394107</t>
         </is>
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31318,37 +31318,37 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NIMRA MOHSIN PATHAN</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8140864087</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KADAR SHAH NI NAL</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L468" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31384,37 +31384,37 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FAIZAN HUSAIN SHAIKH</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8000435667</t>
         </is>
       </c>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RUSTAMPURA</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAGRAMPURA</t>
         </is>
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32102,37 +32102,37 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AJIJA ZAHIR SHAIKH</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825185512</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHIMANI TEKARO JUNA DEPO</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L480" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32234,37 +32234,37 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARISH AZAHARUDDIN MUJAWAR</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9909812786</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR TANTWAD MASJID</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32300,37 +32300,37 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ARISH AZAHARUDDIN MUJAWAR</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9909812786</t>
         </is>
       </c>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NEAR TANTWAD MASJID</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GOPIPURA</t>
         </is>
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32564,37 +32564,37 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANAYA MO.AZHAR SHAIKH</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9724345673</t>
         </is>
       </c>
       <c r="I487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395001</t>
         </is>
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NANPURA</t>
         </is>
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32894,37 +32894,37 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VIANSH DIVYESHKUMAR SONDARVA</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825120985</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ZAMPA BAZAR</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L492" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33784,7 +33784,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34630,37 +34630,37 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOUMAN SAIYED ALI SAIYED</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9327540050</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYEDPURA</t>
         </is>
       </c>
       <c r="K518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>392003</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=20)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35482,37 +35482,37 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOMAN MOHSIN PINJARI</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9879049881</t>
         </is>
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394210</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LIMBAYAT</t>
         </is>
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35746,42 +35746,42 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RABIYA JAFARKHAN PATHAN</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9979551351</t>
         </is>
       </c>
       <c r="I535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M535" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N535" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>UMARWADA</t>
+        </is>
+      </c>
+      <c r="M535" s="10" t="inlineStr">
+        <is>
+          <t>anganwadi na 2 yers complete nathi</t>
+        </is>
+      </c>
+      <c r="N535" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -36302,7 +36302,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36930,37 +36930,37 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AJIJA ZAHIR SHAIKH</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9825185512</t>
         </is>
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHIMANI TEKARO JUNA DEPO</t>
         </is>
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37194,37 +37194,37 @@
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AHMED YAKUB MOTIWALA</t>
         </is>
       </c>
       <c r="H557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>7203078688</t>
         </is>
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395009</t>
         </is>
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ADAJAN</t>
         </is>
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -40952,42 +40952,42 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIIMA SAMIR PATEL</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8347012249</t>
         </is>
       </c>
       <c r="I614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>KOSAD</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>394107</t>
         </is>
       </c>
       <c r="L614" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M614" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
-        </is>
-      </c>
-      <c r="N614" s="9" t="inlineStr">
-        <is>
-          <t>ERROR</t>
+          <t>KOSAD</t>
+        </is>
+      </c>
+      <c r="M614" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N614" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -43090,7 +43090,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43522,37 +43522,37 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RIDAZAHRA MOHAMMAD YUSUF PATHAN</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9712007037</t>
         </is>
       </c>
       <c r="I653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395002</t>
         </is>
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UMARWADA</t>
         </is>
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43816,7 +43816,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43918,37 +43918,37 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NOOR FATEMA MO TOFIK MANSURI</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8460333425</t>
         </is>
       </c>
       <c r="I659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MURAGVAN TEKRA</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BEGAMPURA</t>
         </is>
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44464,7 +44464,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45094,37 +45094,37 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ANABIA SALMAN SHAIKH</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>9687908092</t>
         </is>
       </c>
       <c r="I677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>GIRL</t>
         </is>
       </c>
       <c r="J677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SHAHPORE</t>
         </is>
       </c>
       <c r="K677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395003</t>
         </is>
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SAIYADPURA</t>
         </is>
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45256,7 +45256,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45490,37 +45490,37 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ABHAY ASHOK PENDHARKAR</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>8141172225</t>
         </is>
       </c>
       <c r="I683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BOY</t>
         </is>
       </c>
       <c r="J683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATAR</t>
         </is>
       </c>
       <c r="K683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>395017</t>
         </is>
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BHATAR</t>
         </is>
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45652,7 +45652,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47278,14 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N710" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="M710" s="6" t="inlineStr">
+        <is>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ બીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
+        </is>
+      </c>
+      <c r="N710" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47280,7 +47280,7 @@
       </c>
       <c r="M710" s="6" t="inlineStr">
         <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ બીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
+          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ  ત્રીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
         </is>
       </c>
       <c r="N710" s="7" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -47278,14 +47278,14 @@
           <t>SALABATPURA</t>
         </is>
       </c>
-      <c r="M710" s="6" t="inlineStr">
-        <is>
-          <t>આપનું આ ફોર્મ જીલ્લા કક્ષાએ મંજુર (approve) કરેલ છે.આપનો RTE હેઠળ  ત્રીજા રાઉન્ડમાં પ્રવેશ શક્ય બનેલ નથી.</t>
-        </is>
-      </c>
-      <c r="N710" s="7" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
+      <c r="M710" s="10" t="inlineStr">
+        <is>
+          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
+        </is>
+      </c>
+      <c r="N710" s="11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,11 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -131,12 +126,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -942,37 +931,37 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD SHEHZAD SAJIDBHAI SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>6353938435</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1202,37 +1191,37 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>RUMAIYSHA IMRANKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>9978260385</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>BEGUMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1268,42 +1257,42 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>HASHMIRA CHANDKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>8460673067</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>BHATHENA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -1924,37 +1913,37 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>MAHERA SALIM SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>9033552557</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2118,37 +2107,37 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -6662,37 +6651,37 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ALI SARFARAZKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>8758147466</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6728,37 +6717,37 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>RAIHAN SAEED PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>7405759272</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>rander</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -8176,37 +8165,37 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8242,37 +8231,37 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBER MOHAMAD IFTIKHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>9898957851</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9496,37 +9485,37 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>ALIAN MO.ARIF ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H137" s="5" t="inlineStr">
         <is>
-          <t>8488990883</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J137" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9694,37 +9683,37 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AYAN MOHAMMED FUZEL MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
         <is>
-          <t>9879814246</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>TURKIWAD MUGLISARA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>NANAVAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -10156,37 +10145,37 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>ASHMIRA MOHMAD TAUSIF MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H147" s="5" t="inlineStr">
         <is>
-          <t>6354501628</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J147" s="5" t="inlineStr">
         <is>
-          <t>VARYAVI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10618,37 +10607,37 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>UMMEHAANI ASHFAQUE SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H154" s="5" t="inlineStr">
         <is>
-          <t>8160140266</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>DUMBHAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10882,37 +10871,37 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H158" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10948,37 +10937,37 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA SIRAJUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H159" s="5" t="inlineStr">
         <is>
-          <t>8087798621</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>VOHRAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11674,37 +11663,37 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED SAAD MOHAMMED SAKIR JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>9825956199</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>RANITALAW</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11740,37 +11729,37 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED ZAKI MOHAMMEDTABREZ MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>9173442244</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12070,37 +12059,37 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12136,37 +12125,37 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAMZA MOHAMMAD JUNED MASTER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>9638193923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>MOMNAVAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12334,37 +12323,37 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>AFIYA ASIFMIYA KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>9925523296</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13324,37 +13313,37 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>AAYAT IMRAN SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>9879068344</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14508,37 +14497,37 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>INAYA IMRAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H213" s="5" t="inlineStr">
         <is>
-          <t>7990106539</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -16292,37 +16281,37 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED AAZAM MOHAMMED SIDDIK SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
         <is>
-          <t>9601903640</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA MOMNAWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K240" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16622,37 +16611,37 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMED GULAHMED PANWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H245" s="5" t="inlineStr">
         <is>
-          <t>7405251413</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>JILANI TOWER ADAJAN PATIYA RANDER ROAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K245" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -17086,37 +17075,37 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>NABILA BANU AHMED NOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H252" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K252" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L252" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17152,37 +17141,37 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>NABILABANU AHMEDNOOR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
         <is>
-          <t>8141079302</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K253" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17610,37 +17599,37 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ARSH MO. RIYAZ MALEK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H260" s="5" t="inlineStr">
         <is>
-          <t>9727048923</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>SACHIN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K260" s="5" t="inlineStr">
         <is>
-          <t>394230</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L260" s="5" t="inlineStr">
         <is>
-          <t>SURAT CITY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18398,37 +18387,37 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>SAFWAN ABDUR RAHMAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H272" s="5" t="inlineStr">
         <is>
-          <t>9898377514</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L272" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19454,37 +19443,37 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>HAMJA SAKIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H288" s="5" t="inlineStr">
         <is>
-          <t>9510628797</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>395023</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L288" s="5" t="inlineStr">
         <is>
-          <t>BHESTAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19784,37 +19773,37 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD BURAK HUSAIN MO.IMRAN ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H293" s="5" t="inlineStr">
         <is>
-          <t>9898710533</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>RAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K293" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20378,37 +20367,37 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H302" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K302" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L302" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20444,37 +20433,37 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>BADRUDOJA MOHAMMAD SARTAJ RAEEN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr">
         <is>
-          <t>9265929679</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>BAVASIDI TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K303" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21034,37 +21023,37 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD ZUBAIR ABDUL HAMID SHAH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H312" s="5" t="inlineStr">
         <is>
-          <t>9510956369</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J312" s="5" t="inlineStr">
         <is>
-          <t>KADARSHAH NI NAAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K312" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21364,37 +21353,37 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>AAHIL ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H317" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K317" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21430,37 +21419,37 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>AAHIL MAHMAD ALMAS BHARUCHA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H318" s="5" t="inlineStr">
         <is>
-          <t>7405183050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>SODAGERWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L318" s="5" t="inlineStr">
         <is>
-          <t>SODAGARWAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -22878,37 +22867,37 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>AHMED RAZAKHAN MOHSINKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H340" s="5" t="inlineStr">
         <is>
-          <t>7041239541</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I340" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>NAVSARI BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23208,37 +23197,37 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>MANTASHA BANO MOHAMMAD FAZAL MANYAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H345" s="5" t="inlineStr">
         <is>
-          <t>8401189493</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K345" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23472,37 +23461,37 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD NOMAN NAVIDANJUM RANGREJ</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>9081019408</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23736,37 +23725,37 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>ZAINAB IKBALKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H353" s="5" t="inlineStr">
         <is>
-          <t>7016137650</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K353" s="5" t="inlineStr">
         <is>
-          <t>395004</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>KATARGAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -24792,37 +24781,37 @@
       </c>
       <c r="G369" s="5" t="inlineStr">
         <is>
-          <t>ZEENAT MOHAMMAD ALTAF DOBA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H369" s="5" t="inlineStr">
         <is>
-          <t>6359658865</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I369" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K369" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25452,37 +25441,37 @@
       </c>
       <c r="G379" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H379" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I379" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K379" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25518,37 +25507,37 @@
       </c>
       <c r="G380" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD AFAQ MOHAMMAD AZAZ SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H380" s="5" t="inlineStr">
         <is>
-          <t>8460770234</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I380" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K380" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L380" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26768,37 +26757,37 @@
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H399" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I399" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K399" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26900,37 +26889,37 @@
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
-          <t>SHAIKH MAHIRA MOHAMMAD ZUBER ILYAS SHAIKH SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H401" s="5" t="inlineStr">
         <is>
-          <t>9624460325</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I401" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27032,37 +27021,37 @@
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
-          <t>SHAAD ALI FAIZAL JARIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H403" s="5" t="inlineStr">
         <is>
-          <t>9979765038</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I403" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -30064,37 +30053,37 @@
       </c>
       <c r="G449" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD HAARIS MOHAMMAD HAARIS SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H449" s="5" t="inlineStr">
         <is>
-          <t>7802820848</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I449" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>NEAR HAJURI CHAMBERS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K449" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30592,37 +30581,37 @@
       </c>
       <c r="G457" s="5" t="inlineStr">
         <is>
-          <t>MOHAMMAD RUHAN ABDUL RASHID MESANIYA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H457" s="5" t="inlineStr">
         <is>
-          <t>9586110486</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I457" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J457" s="5" t="inlineStr">
         <is>
-          <t>Bela Industrial Estate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K457" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30856,37 +30845,37 @@
       </c>
       <c r="G461" s="5" t="inlineStr">
         <is>
-          <t>UMAIR AYAZUDDIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H461" s="5" t="inlineStr">
         <is>
-          <t>9998709823</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I461" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31120,37 +31109,37 @@
       </c>
       <c r="G465" s="5" t="inlineStr">
         <is>
-          <t>SHIFA IRFAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H465" s="5" t="inlineStr">
         <is>
-          <t>9714226593</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I465" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K465" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31318,37 +31307,37 @@
       </c>
       <c r="G468" s="5" t="inlineStr">
         <is>
-          <t>NIMRA MOHSIN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H468" s="5" t="inlineStr">
         <is>
-          <t>8140864087</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I468" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J468" s="5" t="inlineStr">
         <is>
-          <t>KADAR SHAH NI NAL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K468" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L468" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31384,37 +31373,37 @@
       </c>
       <c r="G469" s="5" t="inlineStr">
         <is>
-          <t>FAIZAN HUSAIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H469" s="5" t="inlineStr">
         <is>
-          <t>8000435667</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I469" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J469" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K469" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32102,37 +32091,37 @@
       </c>
       <c r="G480" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H480" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I480" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J480" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K480" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L480" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32234,37 +32223,37 @@
       </c>
       <c r="G482" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H482" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I482" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J482" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K482" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L482" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32300,37 +32289,37 @@
       </c>
       <c r="G483" s="5" t="inlineStr">
         <is>
-          <t>ARISH AZAHARUDDIN MUJAWAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H483" s="5" t="inlineStr">
         <is>
-          <t>9909812786</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I483" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J483" s="5" t="inlineStr">
         <is>
-          <t>NEAR TANTWAD MASJID</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K483" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>GOPIPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32564,37 +32553,37 @@
       </c>
       <c r="G487" s="5" t="inlineStr">
         <is>
-          <t>ANAYA MO.AZHAR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H487" s="5" t="inlineStr">
         <is>
-          <t>9724345673</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I487" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K487" s="5" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>NANPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32894,37 +32883,37 @@
       </c>
       <c r="G492" s="5" t="inlineStr">
         <is>
-          <t>VIANSH DIVYESHKUMAR SONDARVA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H492" s="5" t="inlineStr">
         <is>
-          <t>9825120985</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I492" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J492" s="5" t="inlineStr">
         <is>
-          <t>ZAMPA BAZAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K492" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L492" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -34630,37 +34619,37 @@
       </c>
       <c r="G518" s="5" t="inlineStr">
         <is>
-          <t>NOUMAN SAIYED ALI SAIYED</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H518" s="5" t="inlineStr">
         <is>
-          <t>9327540050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I518" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J518" s="5" t="inlineStr">
         <is>
-          <t>SAIYEDPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K518" s="5" t="inlineStr">
         <is>
-          <t>392003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L518" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35482,37 +35471,37 @@
       </c>
       <c r="G531" s="5" t="inlineStr">
         <is>
-          <t>NOMAN MOHSIN PINJARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H531" s="5" t="inlineStr">
         <is>
-          <t>9879049881</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I531" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K531" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>LIMBAYAT</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35746,42 +35735,42 @@
       </c>
       <c r="G535" s="5" t="inlineStr">
         <is>
-          <t>RABIYA JAFARKHAN PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H535" s="5" t="inlineStr">
         <is>
-          <t>9979551351</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I535" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K535" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
-        </is>
-      </c>
-      <c r="M535" s="10" t="inlineStr">
-        <is>
-          <t>anganwadi na 2 yers complete nathi</t>
-        </is>
-      </c>
-      <c r="N535" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M535" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N535" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -36930,37 +36919,37 @@
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
-          <t>AJIJA ZAHIR SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H553" s="5" t="inlineStr">
         <is>
-          <t>9825185512</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J553" s="5" t="inlineStr">
         <is>
-          <t>CHIMANI TEKARO JUNA DEPO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K553" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37194,37 +37183,37 @@
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
-          <t>AHMED YAKUB MOTIWALA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H557" s="5" t="inlineStr">
         <is>
-          <t>7203078688</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K557" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>ADAJAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37656,37 +37645,37 @@
       </c>
       <c r="G564" s="5" t="inlineStr">
         <is>
-          <t>AAYAT MOHAMMAD ASHRAF KHARADI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H564" s="5" t="inlineStr">
         <is>
-          <t>8849059910</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I564" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J564" s="5" t="inlineStr">
         <is>
-          <t>OPP. ALVI ROW HOUSE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K564" s="5" t="inlineStr">
         <is>
-          <t>395009</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L564" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37854,37 +37843,37 @@
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
-          <t>AISHA IMRAN MANSUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H567" s="5" t="inlineStr">
         <is>
-          <t>7016269517</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K567" s="5" t="inlineStr">
         <is>
-          <t>395005</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>RANDER</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -39236,42 +39225,42 @@
       </c>
       <c r="G588" s="5" t="inlineStr">
         <is>
-          <t>ASHHAR MOHAMMED NASIM ANSARI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H588" s="5" t="inlineStr">
         <is>
-          <t>8264969600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I588" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J588" s="5" t="inlineStr">
         <is>
-          <t>UNN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K588" s="5" t="inlineStr">
         <is>
-          <t>394210</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L588" s="5" t="inlineStr">
         <is>
-          <t>Unn</t>
-        </is>
-      </c>
-      <c r="M588" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N588" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M588" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N588" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -40622,42 +40611,42 @@
       </c>
       <c r="G609" s="5" t="inlineStr">
         <is>
-          <t>HASNAIN ISTIYAK SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H609" s="5" t="inlineStr">
         <is>
-          <t>9586438778</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I609" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J609" s="5" t="inlineStr">
         <is>
-          <t>SHERALIBAVA NI DARGAH NO VISHTAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K609" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
-        </is>
-      </c>
-      <c r="M609" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N609" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M609" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N609" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -40952,42 +40941,42 @@
       </c>
       <c r="G614" s="5" t="inlineStr">
         <is>
-          <t>SAIIMA SAMIR PATEL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H614" s="5" t="inlineStr">
         <is>
-          <t>8347012249</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I614" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K614" s="5" t="inlineStr">
         <is>
-          <t>394107</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L614" s="5" t="inlineStr">
         <is>
-          <t>KOSAD</t>
-        </is>
-      </c>
-      <c r="M614" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N614" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M614" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N614" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -43522,37 +43511,37 @@
       </c>
       <c r="G653" s="5" t="inlineStr">
         <is>
-          <t>RIDAZAHRA MOHAMMAD YUSUF PATHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H653" s="5" t="inlineStr">
         <is>
-          <t>9712007037</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I653" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K653" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43918,37 +43907,37 @@
       </c>
       <c r="G659" s="5" t="inlineStr">
         <is>
-          <t>NOOR FATEMA MO TOFIK MANSURI</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H659" s="5" t="inlineStr">
         <is>
-          <t>8460333425</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I659" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J659" s="5" t="inlineStr">
         <is>
-          <t>MURAGVAN TEKRA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K659" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>BEGAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -45094,37 +45083,37 @@
       </c>
       <c r="G677" s="5" t="inlineStr">
         <is>
-          <t>ANABIA SALMAN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H677" s="5" t="inlineStr">
         <is>
-          <t>9687908092</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I677" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J677" s="5" t="inlineStr">
         <is>
-          <t>SHAHPORE</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K677" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>SAIYADPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45490,37 +45479,37 @@
       </c>
       <c r="G683" s="5" t="inlineStr">
         <is>
-          <t>ABHAY ASHOK PENDHARKAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H683" s="5" t="inlineStr">
         <is>
-          <t>8141172225</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I683" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K683" s="5" t="inlineStr">
         <is>
-          <t>395017</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>BHATAR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45820,37 +45809,37 @@
       </c>
       <c r="G688" s="5" t="inlineStr">
         <is>
-          <t>MAHERABANU AMIN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H688" s="5" t="inlineStr">
         <is>
-          <t>9974238362</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I688" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J688" s="5" t="inlineStr">
         <is>
-          <t>SAHARADARVAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K688" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L688" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -46018,37 +46007,37 @@
       </c>
       <c r="G691" s="5" t="inlineStr">
         <is>
-          <t>AEMAN KAMIL SHEKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H691" s="5" t="inlineStr">
         <is>
-          <t>7777993155</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I691" s="5" t="inlineStr">
         <is>
-          <t>GIRL</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J691" s="5" t="inlineStr">
         <is>
-          <t>SAHARA DAEWAJA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K691" s="5" t="inlineStr">
         <is>
-          <t>395010</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>UMARWADA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46274,42 +46263,42 @@
       </c>
       <c r="G695" s="5" t="inlineStr">
         <is>
-          <t>ARAV SURESH RATHOD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H695" s="5" t="inlineStr">
         <is>
-          <t>9825274436</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I695" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J695" s="5" t="inlineStr">
         <is>
-          <t>MALBARI SAHEB NO TEKRO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K695" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L695" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
-        </is>
-      </c>
-      <c r="M695" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N695" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M695" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N695" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
@@ -47118,37 +47107,37 @@
       </c>
       <c r="G708" s="5" t="inlineStr">
         <is>
-          <t>SUFIYANKHAN IRFAN KHAN</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H708" s="5" t="inlineStr">
         <is>
-          <t>8799617761</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I708" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J708" s="5" t="inlineStr">
         <is>
-          <t>RUSTAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K708" s="5" t="inlineStr">
         <is>
-          <t>395002</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L708" s="5" t="inlineStr">
         <is>
-          <t>SAGRAMPURA</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>આપે આ ફોર્મ કેન્સલ કરેલ છે.</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47250,42 +47239,42 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>SHAHID HUSAIN MUJAFFARHUSEN SHAIKH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H710" s="5" t="inlineStr">
         <is>
-          <t>6351802600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I710" s="5" t="inlineStr">
         <is>
-          <t>BOY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J710" s="5" t="inlineStr">
         <is>
-          <t>Kamela Main Road,Salabatpura,Surat</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K710" s="5" t="inlineStr">
         <is>
-          <t>395003</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L710" s="5" t="inlineStr">
         <is>
-          <t>SALABATPURA</t>
-        </is>
-      </c>
-      <c r="M710" s="10" t="inlineStr">
-        <is>
-          <t>આપે આ ફોર્મ કન્ફર્મ કરેલ નથી</t>
-        </is>
-      </c>
-      <c r="N710" s="11" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M710" s="8" t="inlineStr">
+        <is>
+          <t>Status not found</t>
+        </is>
+      </c>
+      <c r="N710" s="9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>Status not found</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55857220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559200a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5591c700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55936c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559208b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e81c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e85b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e8970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547dba00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547dbe80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547db910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dcd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e84f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55944b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5591bd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558515e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559fb8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e82e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54748ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54210c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54210520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a3a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559441c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55944340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54748550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a542939a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558e93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547f1700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b60a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b3e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b6250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b35e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b37c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544a6d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547f1c40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54293b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479aaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543813d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b64c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547b0910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558ea640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b0700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b6580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559880d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544cb0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437da90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b3be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559f0f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437deb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437d730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466a1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466a4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466aa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466af70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466ad60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559423a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b72e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b0b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b72b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544cb250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55857220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559200a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5591c700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55936c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55920190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559208b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e81c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e85b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e8970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547dba00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547dbe80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547db910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dc640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545dcd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e84f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55944b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5591bd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558515e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559fb8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e82e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a541e8850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547e2850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54748ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54210c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54210520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54799af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479a3a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559441c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a545e3040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55944340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55988ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54748550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a542939a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558e93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547f1700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b60a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b3e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b6250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b35e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b37c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544a6d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547f1c40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54293b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5479aaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543813d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55851070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b64c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a547b0910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a558ea640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b0700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b6580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559880d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544cb0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437da90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b3be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559f0f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437deb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437d730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466a1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466a4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466aa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466af70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5466ad60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a5437dca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a55950f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a54381d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a559423a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b72e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544b0b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b7280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a543b72b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f6a544cb250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe965b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe961f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff16ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff68c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff69c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce19550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f7120030fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff697c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f71200309a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce224c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce2a6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce22fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce223a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce2a4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1b520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce220a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1b2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc189d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff84130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1bfd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc188b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f71200930a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce190d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc189d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe961f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c84f100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c84fcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc181f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79ce80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79c970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79ccd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cdf9f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79c340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca4aeb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca465b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca467c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca4ab50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca426a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca505b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca513d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca518e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca51df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca51af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca515e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca56160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca3dd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca428e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca201c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce36ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49dac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce36640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4cb2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49c9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4af850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49d400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc958b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc956a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc95490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4af340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4ae820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4aefa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca3d100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49a1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 404 Client Error: Not Found for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4ae5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe965b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe961f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b6a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff16ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff68c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff69c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce19550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f7120030fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff697c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f817c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f71200309a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce224c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce2a6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce22fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8bbe0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce223a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce2a4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8bdf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1b520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce220a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740b93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1b2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f81310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e06a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e07c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc189d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffab80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ff84130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c61c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce1bfd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffac40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc188b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d39d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f71200930a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474199520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce16d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d34f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47412c9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47412cac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce190d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4744e5be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc189d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe96e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711fe961f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c84f100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db2520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c84fcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc181f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffafd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474110220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470e113a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc18ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d36a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc20670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db2a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47411f100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa5e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7baf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740edd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47411f460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740cf6a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc21070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740cf640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79ce80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470def2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79c970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79ccd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cdf9f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c67c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f0cc10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c79c340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470def880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca4aeb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b760&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca465b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca467c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470deedf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca4ab50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dee9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca426a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca505b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470deeca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca50e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470ded070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca513d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca518e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca51df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c96d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca51af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca515e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca56160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca3dd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b3a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca428e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca201c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470ded5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce36ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474088a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca20130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407a4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49dac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407a730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ce36640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca46280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4cb2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d510d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4c7fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d51490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49c9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407aa60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4af850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49d400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c6f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cd87b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f0edc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc958b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc956a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47418d3d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711cc95490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca42f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c91c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4af340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4ae820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7e50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4aefa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47416dca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711ca3d100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c49a1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f711c4ae5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d285b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d310a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b6a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d28b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d312b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae6d790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefca60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae7b850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae798b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f817c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d286a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d281c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8bbe0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae6dcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d401f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8bdf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af3be80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f8b4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d317f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740b93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d407f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741f0550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d401c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f81310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e06a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af75c40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e07c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcb20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcb50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d37370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffab80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c61c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffac40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d4afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d3280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d39d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d4a430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474199520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d34f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af8cbe0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47412c9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa29a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47412cac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae8d880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4744e5be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d44b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefc940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208724070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db2520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffafd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474110220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470e113a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd8670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae8de20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740d36a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae9e670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae9ee50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db2a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af758b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd8be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47411f100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920870c130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc473ffa5e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7baf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740edd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d317f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740ee2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47411f460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740cf6a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d315b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740cf640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470def2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3cf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3cbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa25e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c67c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208938b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f0cc10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b7f5e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d0de20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470def880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b760&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470deedf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dee9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a322b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae79670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208930490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470deeca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d310d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470ded070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae3b100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c96d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834bbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a360a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f7b0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a362e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b3a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470ded5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a368b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740e0fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc474088a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aea2e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dd5dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aea2be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407a4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae2e520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407a730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc7a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eabb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c34910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d35b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d510d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d51490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088b80a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47407aa60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4740c6f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaf70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470c4b370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b404f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470f0edc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2bb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47418d3d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c91c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc4741c9880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a369a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470db7e50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaa90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc47416dca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470d7b9d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7fc470dc8580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af40ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d285b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d310a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d28b50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d312b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae6d790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefca60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae7b850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae798b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d286a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d281c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40d00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae6dcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d401f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af3be80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d317f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d407f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d401c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d40550&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af75c40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcb20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcb50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d37370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31d60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d4afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d4a430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af8cbe0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa29a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae8d880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b19b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefcee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aefc940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208724070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd8670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae8de20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae9e670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae9ee50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af758b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd8be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208cd87c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920870c130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1ac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d317f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208ad1070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d315b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3cf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3cbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa25e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208938b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b7f5e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d0de20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af4b520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a322b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae79670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208930490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d310d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d3c790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae3b100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834b820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920834bbb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920afa2a00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208d31400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a360a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a362e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a368b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a36fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aea2e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920aea2be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920ae2e520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eabb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d35b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088b80a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b40280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaf70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208b404f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086ea6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2bb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92087e2910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9208a369a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92086eaa90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f92088d3610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f920af40ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>Status not found</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Read timed out. (read timeout=15)</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
